--- a/excels/Tablas capítulo 5.xlsx
+++ b/excels/Tablas capítulo 5.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kennethram\Documents\GitHub\PropuestaProyectoDeCarrera\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{146C0C7B-C21C-4CC8-BFD9-78581E1A4CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA7990A-9CDA-470F-99FB-97E12C732F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla 5.1 Funcionales" sheetId="1" r:id="rId1"/>
     <sheet name="Tabla 5.2 No funcionales" sheetId="2" r:id="rId2"/>
+    <sheet name="Tabla 5.3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>Tabla 5.1. Requerimientos funcionales identificados</t>
   </si>
@@ -137,16 +138,80 @@
   </si>
   <si>
     <t>Fuente: Elaboración propia, con base en las necesidades institucionales y las condiciones de diseño de SIRCOVA.</t>
+  </si>
+  <si>
+    <t>Fuente: Los autores mediante Microsoft Excel</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>HU-56 a HU-60</t>
+  </si>
+  <si>
+    <t>Finalización del proyecto</t>
+  </si>
+  <si>
+    <t>HU-45 a HU-55</t>
+  </si>
+  <si>
+    <t>Sprint 5. Reportes, alertas y auditoría</t>
+  </si>
+  <si>
+    <t>HU-35 a HU-44</t>
+  </si>
+  <si>
+    <t>Sprint 4. Indicadores, análisis y visualización</t>
+  </si>
+  <si>
+    <t>HU-24 a HU-34</t>
+  </si>
+  <si>
+    <t>Sprint 3. Validación, revisión y cierre</t>
+  </si>
+  <si>
+    <t>HU-12 a HU-23</t>
+  </si>
+  <si>
+    <t>Sprint 2. Configuración dinámica y registro de producción</t>
+  </si>
+  <si>
+    <t>HU-01 a HU-11</t>
+  </si>
+  <si>
+    <t>Sprint 1. Acceso, usuarios y catálogos básicos</t>
+  </si>
+  <si>
+    <t>Puntos de historia</t>
+  </si>
+  <si>
+    <t>Historias o tareas</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>DISTRIBUCIÓN DE HISTORIAS DE USUARIO Y ACTIVIDADES POR SPRINT</t>
+  </si>
+  <si>
+    <t>Tabla 5.3 Distribución de historias de usuario y actividades por sprint</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -207,8 +272,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF3F5874"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF3F5874"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,8 +347,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F5D95"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -256,52 +371,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{71B0A56D-7504-444F-A6B7-F8946CF7CBCE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -531,20 +697,20 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="2:3" ht="21" customHeight="1">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="2:3" ht="15" customHeight="1">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="2:3" ht="35.25" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="2:3" ht="21" customHeight="1">
       <c r="B5" s="1"/>
@@ -627,10 +793,10 @@
       <c r="C15" s="1"/>
     </row>
     <row r="16" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="12"/>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="1"/>
@@ -669,17 +835,17 @@
       <c r="B2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="2:3" ht="15" customHeight="1">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="2:3" ht="35.25" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="2:3" ht="21" customHeight="1">
       <c r="B5" s="1"/>
@@ -710,34 +876,34 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="36.75" customHeight="1">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="36.75" customHeight="1">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="36.75" customHeight="1">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="36.75" customHeight="1">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>35</v>
       </c>
     </row>
@@ -746,10 +912,10 @@
       <c r="C13" s="1"/>
     </row>
     <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="12"/>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="1"/>
@@ -771,4 +937,135 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDE31DB-9B25-4466-A54D-C36CE357D9FF}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="34.19921875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" style="14" customWidth="1"/>
+    <col min="4" max="16384" width="8" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="24" customHeight="1">
+      <c r="A1" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+    </row>
+    <row r="3" spans="1:3" ht="37.950000000000003" customHeight="1">
+      <c r="A3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+    </row>
+    <row r="5" spans="1:3" ht="31.2" customHeight="1">
+      <c r="A5" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="22">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="19">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A8" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="19">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A10" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="22">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="34.049999999999997" customHeight="1">
+      <c r="A12" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="17">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="24" customHeight="1">
+      <c r="A14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
 </file>